--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -662,12 +662,11 @@
           <t>NSE:INOXWIND26AUG75PE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:20:43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,101 @@
           <t>2026-08-12 09:20:43</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:23:12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2010.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I3" t="n">
+        <v>31</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="K3" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="L3" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="M3" t="n">
+        <v>59.54</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1612</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="U3" t="n">
+        <v>32</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:BAJAJFINSV26AUG2020CE</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -756,12 +756,11 @@
           <t>NSE:BAJAJFINSV26AUG2020CE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:25:41</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,6 +761,101 @@
           <t>2026-08-12 09:25:41</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:30:45</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="H4" t="n">
+        <v>420</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="L4" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="M4" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3968</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="S4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="U4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:NATIONALUM26AUG420CE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,12 +850,101 @@
           <t>NSE:NATIONALUM26AUG420CE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:42:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3553.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I5" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="J5" t="n">
+        <v>96.26000000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>156.05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>172.97</v>
+      </c>
+      <c r="M5" t="n">
+        <v>195.53</v>
+      </c>
+      <c r="N5" t="n">
+        <v>391</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="S5" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="U5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:BSE26AUG3600PE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,12 +939,100 @@
           <t>NSE:BSE26AUG3600PE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:45:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>350</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="L6" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4032</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="S6" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="U6" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:PATANJALI26AUG350PE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,6 +1033,101 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:10:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2660.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2650</v>
+      </c>
+      <c r="I7" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>68.41</v>
+      </c>
+      <c r="L7" t="n">
+        <v>76.73</v>
+      </c>
+      <c r="M7" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="N7" t="n">
+        <v>916</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="U7" t="n">
+        <v>35</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:WAAREEENER26AUG2650PE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1122,12 +1122,11 @@
           <t>NSE:WAAREEENER26AUG2650PE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:12:51</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1122,11 +1122,7 @@
           <t>NSE:WAAREEENER26AUG2650PE</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-12 10:12:51</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1122,7 +1122,11 @@
           <t>NSE:WAAREEENER26AUG2650PE</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:35:19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,6 +1127,101 @@
           <t>2026-08-12 10:35:19</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:37:29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>108.61</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H8" t="n">
+        <v>110</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14836</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="S8" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>46.27</v>
+      </c>
+      <c r="U8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:VMM26AUG110PE</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1033,6 +1033,16 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:41:16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1216,12 +1226,6 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,6 +1226,11 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:44:03</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,6 +1231,101 @@
           <t>2026-08-12 10:44:03</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:50:31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H9" t="n">
+        <v>118</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15923</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="U9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:PNB26AUG118CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,11 +1226,7 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-12 10:44:03</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1320,12 +1316,6 @@
           <t>NSE:PNB26AUG118CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,7 +1226,11 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:59:15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,11 +1226,7 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-12 10:59:15</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,7 +1226,6 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1314,6 +1313,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:PNB26AUG118CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:07:55</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1315,11 +1315,7 @@
           <t>NSE:PNB26AUG118CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-12 11:07:55</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1315,7 +1315,11 @@
           <t>NSE:PNB26AUG118CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:12:15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1320,6 +1320,101 @@
           <t>2026-08-12 11:12:15</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:25:12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>46600</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>46500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1025.05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>669.39</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1342.61</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1533.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1787.19</v>
+      </c>
+      <c r="N10" t="n">
+        <v>48</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="S10" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:BOSCHLTD26AUG46500CE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,6 +1226,11 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:29:37</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1409,12 +1414,6 @@
           <t>NSE:BOSCHLTD26AUG46500CE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,11 +1226,7 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-12 11:29:37</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,7 +1226,6 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1410,6 +1409,101 @@
           <t>NSE:BOSCHLTD26AUG46500CE</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:33:57</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3519.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I11" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="J11" t="n">
+        <v>96.26000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>156.05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>172.97</v>
+      </c>
+      <c r="M11" t="n">
+        <v>195.53</v>
+      </c>
+      <c r="N11" t="n">
+        <v>391</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="S11" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:BSE26AUG3600PE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,12 +1498,101 @@
           <t>NSE:BSE26AUG3600PE</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:46:27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>839.15</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="H12" t="n">
+        <v>840</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="K12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="M12" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3831</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="U12" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:MARICO26AUG840CE</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1587,12 +1587,11 @@
           <t>NSE:MARICO26AUG840CE</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:49:01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1226,6 +1226,16 @@
           <t>NSE:VMM26AUG110PE</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:56:05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1038,9 +1038,14 @@
           <t>2026-08-12 10:41:16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-08-12 12:39:05</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,6 +1048,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-12 12:54:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,11 +1048,7 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-12 12:54:30</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,7 +1048,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-12 13:02:11</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,11 +1048,7 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-12 13:02:11</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,7 +1048,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1237,9 +1236,14 @@
           <t>2026-08-12 11:56:05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-08-12 13:06:05</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,6 +1048,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-12 13:09:40</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,11 +1048,7 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-12 13:09:40</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,7 +1048,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1606,6 +1605,16 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:MARICO26AUG840CE</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-12 13:15:13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1241,9 +1241,14 @@
           <t>2026-08-12 13:06:05</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-12 13:19:26</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,6 +1627,101 @@
           <t>2026-08-12 11:49:01</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-12 13:30:07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>376</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9615</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="S13" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="U13" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26AUG376PE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1716,12 +1716,11 @@
           <t>NSE:INDUSTOWER26AUG376PE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-12 13:32:36</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1523,6 +1523,16 @@
           <t>NSE:BSE26AUG3600PE</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-12 14:07:05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1731,6 +1731,101 @@
           <t>2026-08-12 13:32:36</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-12 14:55:26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1080.15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="K14" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="L14" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2262</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="S14" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="U14" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:HINDALCO26AUG1080CE</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -1048,6 +1048,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-12 14:58:07</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1820,12 +1825,6 @@
           <t>NSE:HINDALCO26AUG1080CE</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -939,6 +939,16 @@
           <t>NSE:BSE26AUG3600PE</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:41:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-12 09:45:00</t>

--- a/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/signals_2026-08-12.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:INOXWIND26AUG75PE</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Closed down ~2.64 (-0.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-12 09:20:43</t>
@@ -756,6 +761,11 @@
           <t>NSE:BAJAJFINSV26AUG2020CE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Closed up ~33.0 (+6.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-12 09:25:41</t>
@@ -850,6 +860,11 @@
           <t>NSE:NATIONALUM26AUG420CE</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Closed down ~10.7 (-15.1% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1152,6 +1167,11 @@
           <t>NSE:WAAREEENER26AUG2650PE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed down ~53.9 (-1.2% from entry)</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-12 10:35:19</t>
@@ -1355,6 +1375,11 @@
           <t>NSE:PNB26AUG118CE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~3.0 (-4.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>2026-08-12 11:12:15</t>
@@ -1449,6 +1474,11 @@
           <t>NSE:BOSCHLTD26AUG46500CE</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Closed down ~980.0 (-4.4% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1741,6 +1771,11 @@
           <t>NSE:INDUSTOWER26AUG376PE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed down ~4.9 (-5.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-12 13:32:36</t>
@@ -1833,6 +1868,11 @@
       <c r="W14" t="inlineStr">
         <is>
           <t>NSE:HINDALCO26AUG1080CE</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Closed down ~19.65 (-11.1% from entry, EOD estimate)</t>
         </is>
       </c>
     </row>
